--- a/Unisport-FutbolDataAcademy/Unisport/ModuloDos/participacion_en_el_juego.xlsx
+++ b/Unisport-FutbolDataAcademy/Unisport/ModuloDos/participacion_en_el_juego.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidvh10/Desktop/Mis Cosas/MASTER UNISPORT/Modulo 2/Trabajos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidvh10/Desktop/Mis Cosas/RepositorioCodigo/Unisport-FutbolDataAcademy/Unisport/ModuloDos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1064BD75-3165-0344-BB32-3B588BC4BB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B93C4C1-5104-4348-A0DB-35DC1A442C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7420" yWindow="2660" windowWidth="28040" windowHeight="17440" xr2:uid="{D01ACE11-2F64-D442-81D6-1A9F9F4A7DB9}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t>Jugador</t>
   </si>
@@ -506,6 +506,9 @@
   </si>
   <si>
     <t>Yan Diomande</t>
+  </si>
+  <si>
+    <t>Mikel Oyarzábal</t>
   </si>
 </sst>
 </file>
@@ -880,7 +883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32C8081-2E1E-E04A-BC92-1E8D2679565E}">
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
@@ -1491,568 +1494,568 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>157</v>
       </c>
       <c r="B24">
-        <v>1733</v>
+        <v>1585</v>
       </c>
       <c r="C24">
-        <v>78.5</v>
+        <v>76.2</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="E24">
-        <v>60</v>
+        <v>57.5</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G24">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H24">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25">
-        <v>644</v>
+        <v>1733</v>
       </c>
       <c r="C25">
-        <v>71.2</v>
+        <v>78.5</v>
       </c>
       <c r="D25">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="E25">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F25">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H25">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26">
-        <v>1582</v>
+        <v>644</v>
       </c>
       <c r="C26">
-        <v>80.8</v>
+        <v>71.2</v>
       </c>
       <c r="D26">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="E26">
-        <v>42.9</v>
+        <v>45</v>
       </c>
       <c r="F26">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G26">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H26">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27">
-        <v>1532</v>
+        <v>1582</v>
       </c>
       <c r="C27">
-        <v>88.5</v>
+        <v>80.8</v>
       </c>
       <c r="D27">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E27">
-        <v>46.5</v>
+        <v>42.9</v>
       </c>
       <c r="F27">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="G27">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H27">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28">
-        <v>1880</v>
+        <v>1532</v>
       </c>
       <c r="C28">
-        <v>90.5</v>
+        <v>88.5</v>
       </c>
       <c r="D28">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E28">
-        <v>66.7</v>
+        <v>46.5</v>
       </c>
       <c r="F28">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G28">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H28">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29">
+        <v>1880</v>
+      </c>
+      <c r="C29">
+        <v>90.5</v>
+      </c>
+      <c r="D29">
         <v>32</v>
       </c>
-      <c r="B29">
-        <v>1091</v>
-      </c>
-      <c r="C29">
-        <v>67.3</v>
-      </c>
-      <c r="D29">
-        <v>69</v>
-      </c>
       <c r="E29">
-        <v>53.5</v>
+        <v>66.7</v>
       </c>
       <c r="F29">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G29">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H29">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30">
-        <v>1063</v>
+        <v>1091</v>
       </c>
       <c r="C30">
-        <v>81.5</v>
+        <v>67.3</v>
       </c>
       <c r="D30">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="E30">
-        <v>43.8</v>
+        <v>53.5</v>
       </c>
       <c r="F30">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G30">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H30">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31">
-        <v>1168</v>
+        <v>1063</v>
       </c>
       <c r="C31">
-        <v>76.3</v>
+        <v>81.5</v>
       </c>
       <c r="D31">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="E31">
-        <v>43.3</v>
+        <v>43.8</v>
       </c>
       <c r="F31">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G31">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H31">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32">
-        <v>1055</v>
+        <v>1168</v>
       </c>
       <c r="C32">
-        <v>85.3</v>
+        <v>76.3</v>
       </c>
       <c r="D32">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="E32">
-        <v>59.4</v>
+        <v>43.3</v>
       </c>
       <c r="F32">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G32">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H32">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33">
-        <v>999</v>
+        <v>1055</v>
       </c>
       <c r="C33">
-        <v>75.8</v>
+        <v>85.3</v>
       </c>
       <c r="D33">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E33">
-        <v>41.7</v>
+        <v>59.4</v>
       </c>
       <c r="F33">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G33">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H33">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34">
-        <v>1910</v>
+        <v>999</v>
       </c>
       <c r="C34">
-        <v>88.9</v>
+        <v>75.8</v>
       </c>
       <c r="D34">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E34">
-        <v>44.4</v>
+        <v>41.7</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G34">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35">
-        <v>635</v>
+        <v>1910</v>
       </c>
       <c r="C35">
-        <v>86.3</v>
+        <v>88.9</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E35">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G35">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H35">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36">
-        <v>959</v>
+        <v>635</v>
       </c>
       <c r="C36">
-        <v>84.3</v>
+        <v>86.3</v>
       </c>
       <c r="D36">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="E36">
-        <v>43.3</v>
+        <v>50</v>
       </c>
       <c r="F36">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G36">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H36">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37">
-        <v>1187</v>
+        <v>959</v>
       </c>
       <c r="C37">
-        <v>83.6</v>
+        <v>84.3</v>
       </c>
       <c r="D37">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="E37">
-        <v>59</v>
+        <v>43.3</v>
       </c>
       <c r="F37">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G37">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H37">
-        <v>62</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38">
-        <v>1607</v>
+        <v>1187</v>
       </c>
       <c r="C38">
-        <v>82.1</v>
+        <v>83.6</v>
       </c>
       <c r="D38">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="E38">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="F38">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G38">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="H38">
-        <v>10</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39">
-        <v>934</v>
+        <v>1607</v>
       </c>
       <c r="C39">
-        <v>78.900000000000006</v>
+        <v>82.1</v>
       </c>
       <c r="D39">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E39">
-        <v>28.6</v>
+        <v>40</v>
       </c>
       <c r="F39">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G39">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H39">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40">
-        <v>1751</v>
+        <v>934</v>
       </c>
       <c r="C40">
-        <v>70.099999999999994</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="D40">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="E40">
-        <v>47.5</v>
+        <v>28.6</v>
       </c>
       <c r="F40">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G40">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H40">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41">
-        <v>1528</v>
+        <v>1751</v>
       </c>
       <c r="C41">
-        <v>88.2</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="D41">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="E41">
-        <v>47.1</v>
+        <v>47.5</v>
       </c>
       <c r="F41">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G41">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H41">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42">
-        <v>759</v>
+        <v>1528</v>
       </c>
       <c r="C42">
-        <v>80.400000000000006</v>
+        <v>88.2</v>
       </c>
       <c r="D42">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E42">
-        <v>38.5</v>
+        <v>47.1</v>
       </c>
       <c r="F42">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G42">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H42">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43">
-        <v>678</v>
+        <v>759</v>
       </c>
       <c r="C43">
-        <v>81.099999999999994</v>
+        <v>80.400000000000006</v>
       </c>
       <c r="D43">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="E43">
-        <v>40.700000000000003</v>
+        <v>38.5</v>
       </c>
       <c r="F43">
         <v>13</v>
       </c>
       <c r="G43">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H43">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44">
-        <v>2004</v>
+        <v>678</v>
       </c>
       <c r="C44">
-        <v>87.2</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="D44">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="E44">
-        <v>41.7</v>
+        <v>40.700000000000003</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G44">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H44">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45">
-        <v>819</v>
+        <v>2004</v>
       </c>
       <c r="C45">
-        <v>79.400000000000006</v>
+        <v>87.2</v>
       </c>
       <c r="D45">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E45">
-        <v>38.5</v>
+        <v>41.7</v>
       </c>
       <c r="F45">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G45">
         <v>13</v>
@@ -2063,441 +2066,441 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>148</v>
+        <v>48</v>
       </c>
       <c r="B46">
-        <v>1416</v>
+        <v>819</v>
       </c>
       <c r="C46">
-        <v>81.8</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="D46">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="E46">
-        <v>52.5</v>
+        <v>38.5</v>
       </c>
       <c r="F46">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="G46">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H46">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>148</v>
       </c>
       <c r="B47">
-        <v>1973</v>
+        <v>1416</v>
       </c>
       <c r="C47">
-        <v>88</v>
+        <v>81.8</v>
       </c>
       <c r="D47">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="E47">
-        <v>62.1</v>
+        <v>52.5</v>
       </c>
       <c r="F47">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="G47">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H47">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B48">
-        <v>1594</v>
+        <v>1973</v>
       </c>
       <c r="C48">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D48">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="E48">
-        <v>56.1</v>
+        <v>62.1</v>
       </c>
       <c r="F48">
+        <v>14</v>
+      </c>
+      <c r="G48">
+        <v>40</v>
+      </c>
+      <c r="H48">
         <v>19</v>
-      </c>
-      <c r="G48">
-        <v>39</v>
-      </c>
-      <c r="H48">
-        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B49">
-        <v>1850</v>
+        <v>1594</v>
       </c>
       <c r="C49">
-        <v>90.3</v>
+        <v>84</v>
       </c>
       <c r="D49">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="E49">
-        <v>63.3</v>
+        <v>56.1</v>
       </c>
       <c r="F49">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G49">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="H49">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B50">
-        <v>508</v>
+        <v>1850</v>
       </c>
       <c r="C50">
-        <v>66.7</v>
+        <v>90.3</v>
       </c>
       <c r="D50">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E50">
-        <v>16.7</v>
+        <v>63.3</v>
       </c>
       <c r="F50">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B51">
-        <v>1258</v>
+        <v>508</v>
       </c>
       <c r="C51">
-        <v>74.8</v>
+        <v>66.7</v>
       </c>
       <c r="D51">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="E51">
-        <v>52.9</v>
+        <v>16.7</v>
       </c>
       <c r="F51">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B52">
-        <v>426</v>
+        <v>1258</v>
       </c>
       <c r="C52">
-        <v>74.400000000000006</v>
+        <v>74.8</v>
       </c>
       <c r="D52">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="E52">
-        <v>60.9</v>
+        <v>52.9</v>
       </c>
       <c r="F52">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G52">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H52">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B53">
-        <v>1212</v>
+        <v>426</v>
       </c>
       <c r="C53">
-        <v>85.4</v>
+        <v>74.400000000000006</v>
       </c>
       <c r="D53">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E53">
-        <v>40</v>
+        <v>60.9</v>
       </c>
       <c r="F53">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G53">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B54">
-        <v>1427</v>
+        <v>1212</v>
       </c>
       <c r="C54">
-        <v>83.6</v>
+        <v>85.4</v>
       </c>
       <c r="D54">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E54">
-        <v>33.299999999999997</v>
+        <v>40</v>
       </c>
       <c r="F54">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G54">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H54">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B55">
-        <v>241</v>
+        <v>1427</v>
       </c>
       <c r="C55">
-        <v>84.1</v>
+        <v>83.6</v>
       </c>
       <c r="D55">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E55">
-        <v>50</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B56">
-        <v>1584</v>
+        <v>241</v>
       </c>
       <c r="C56">
-        <v>85.6</v>
+        <v>84.1</v>
       </c>
       <c r="D56">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E56">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="F56">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G56">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B57">
-        <v>1362</v>
+        <v>1584</v>
       </c>
       <c r="C57">
-        <v>73.900000000000006</v>
+        <v>85.6</v>
       </c>
       <c r="D57">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="E57">
-        <v>34.799999999999997</v>
+        <v>64</v>
       </c>
       <c r="F57">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G57">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H57">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B58">
-        <v>1129</v>
+        <v>1362</v>
       </c>
       <c r="C58">
-        <v>80.2</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="D58">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E58">
-        <v>35.5</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="F58">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G58">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H58">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B59">
-        <v>1331</v>
+        <v>1129</v>
       </c>
       <c r="C59">
-        <v>80.099999999999994</v>
+        <v>80.2</v>
       </c>
       <c r="D59">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E59">
-        <v>56.4</v>
+        <v>35.5</v>
       </c>
       <c r="F59">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H59">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B60">
-        <v>1545</v>
+        <v>1331</v>
       </c>
       <c r="C60">
-        <v>85.6</v>
+        <v>80.099999999999994</v>
       </c>
       <c r="D60">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="E60">
-        <v>51</v>
+        <v>56.4</v>
       </c>
       <c r="F60">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="G60">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H60">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B61">
-        <v>809</v>
+        <v>1545</v>
       </c>
       <c r="C61">
-        <v>83</v>
+        <v>85.6</v>
       </c>
       <c r="D61">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E61">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="F61">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="G61">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H61">
-        <v>14</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62">
-        <v>930</v>
+        <v>809</v>
       </c>
       <c r="C62">
-        <v>72.5</v>
+        <v>83</v>
       </c>
       <c r="D62">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E62">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F62">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G62">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H62">
         <v>14</v>
@@ -2505,2105 +2508,2105 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B63">
-        <v>1862</v>
+        <v>930</v>
       </c>
       <c r="C63">
-        <v>82.5</v>
+        <v>72.5</v>
       </c>
       <c r="D63">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E63">
-        <v>57.8</v>
+        <v>35</v>
       </c>
       <c r="F63">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G63">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H63">
-        <v>48</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64">
-        <v>1235</v>
+        <v>1862</v>
       </c>
       <c r="C64">
-        <v>77.900000000000006</v>
+        <v>82.5</v>
       </c>
       <c r="D64">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="E64">
-        <v>41</v>
+        <v>57.8</v>
       </c>
       <c r="F64">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G64">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H64">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B65">
-        <v>843</v>
+        <v>1235</v>
       </c>
       <c r="C65">
-        <v>88</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="D65">
+        <v>92</v>
+      </c>
+      <c r="E65">
+        <v>41</v>
+      </c>
+      <c r="F65">
+        <v>23</v>
+      </c>
+      <c r="G65">
         <v>28</v>
       </c>
-      <c r="E65">
-        <v>60</v>
-      </c>
-      <c r="F65">
-        <v>12</v>
-      </c>
-      <c r="G65">
-        <v>18</v>
-      </c>
       <c r="H65">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B66">
-        <v>1627</v>
+        <v>843</v>
       </c>
       <c r="C66">
-        <v>85.7</v>
+        <v>88</v>
       </c>
       <c r="D66">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E66">
-        <v>44.8</v>
+        <v>60</v>
       </c>
       <c r="F66">
         <v>12</v>
       </c>
       <c r="G66">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H66">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B67">
-        <v>530</v>
+        <v>1627</v>
       </c>
       <c r="C67">
-        <v>80.2</v>
+        <v>85.7</v>
       </c>
       <c r="D67">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="E67">
-        <v>41.7</v>
+        <v>44.8</v>
       </c>
       <c r="F67">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G67">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H67">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B68">
-        <v>1537</v>
+        <v>530</v>
       </c>
       <c r="C68">
-        <v>81.5</v>
+        <v>80.2</v>
       </c>
       <c r="D68">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="E68">
-        <v>33.299999999999997</v>
+        <v>41.7</v>
       </c>
       <c r="F68">
+        <v>17</v>
+      </c>
+      <c r="G68">
+        <v>12</v>
+      </c>
+      <c r="H68">
         <v>5</v>
-      </c>
-      <c r="G68">
-        <v>54</v>
-      </c>
-      <c r="H68">
-        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B69">
-        <v>1664</v>
+        <v>1537</v>
       </c>
       <c r="C69">
-        <v>90.5</v>
+        <v>81.5</v>
       </c>
       <c r="D69">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E69">
-        <v>45</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="F69">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G69">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="H69">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B70">
-        <v>805</v>
+        <v>1664</v>
       </c>
       <c r="C70">
-        <v>90.2</v>
+        <v>90.5</v>
       </c>
       <c r="D70">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E70">
-        <v>57.1</v>
+        <v>45</v>
       </c>
       <c r="F70">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G70">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="H70">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B71">
-        <v>1004</v>
+        <v>805</v>
       </c>
       <c r="C71">
-        <v>82.3</v>
+        <v>90.2</v>
       </c>
       <c r="D71">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="E71">
+        <v>57.1</v>
+      </c>
+      <c r="F71">
+        <v>7</v>
+      </c>
+      <c r="G71">
         <v>12</v>
       </c>
-      <c r="F71">
-        <v>14</v>
-      </c>
-      <c r="G71">
-        <v>10</v>
-      </c>
       <c r="H71">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B72">
-        <v>698</v>
+        <v>1004</v>
       </c>
       <c r="C72">
-        <v>89.6</v>
+        <v>82.3</v>
       </c>
       <c r="D72">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="E72">
-        <v>37.5</v>
+        <v>12</v>
       </c>
       <c r="F72">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G72">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H72">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B73">
-        <v>1803</v>
+        <v>698</v>
       </c>
       <c r="C73">
-        <v>87.9</v>
+        <v>89.6</v>
       </c>
       <c r="D73">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="E73">
-        <v>48.6</v>
+        <v>37.5</v>
       </c>
       <c r="F73">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G73">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H73">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B74">
-        <v>415</v>
+        <v>1803</v>
       </c>
       <c r="C74">
-        <v>89.2</v>
+        <v>87.9</v>
       </c>
       <c r="D74">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="E74">
-        <v>85.7</v>
+        <v>48.6</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="G74">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H74">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B75">
-        <v>1471</v>
+        <v>415</v>
       </c>
       <c r="C75">
-        <v>71.8</v>
+        <v>89.2</v>
       </c>
       <c r="D75">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="E75">
-        <v>29.4</v>
+        <v>85.7</v>
       </c>
       <c r="F75">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G75">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H75">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B76">
-        <v>569</v>
+        <v>1471</v>
       </c>
       <c r="C76">
-        <v>86.8</v>
+        <v>71.8</v>
       </c>
       <c r="D76">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="E76">
-        <v>57.1</v>
+        <v>29.4</v>
       </c>
       <c r="F76">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="G76">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H76">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B77">
-        <v>1248</v>
+        <v>569</v>
       </c>
       <c r="C77">
-        <v>90.7</v>
+        <v>86.8</v>
       </c>
       <c r="D77">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E77">
-        <v>40</v>
+        <v>57.1</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G77">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B78">
-        <v>316</v>
+        <v>1248</v>
       </c>
       <c r="C78">
-        <v>86.3</v>
+        <v>90.7</v>
       </c>
       <c r="D78">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E78">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F78">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G78">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B79">
-        <v>1757</v>
+        <v>316</v>
       </c>
       <c r="C79">
-        <v>84.2</v>
+        <v>86.3</v>
       </c>
       <c r="D79">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="E79">
-        <v>51.2</v>
+        <v>50</v>
       </c>
       <c r="F79">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G79">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="H79">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B80">
-        <v>544</v>
+        <v>1757</v>
       </c>
       <c r="C80">
-        <v>86.7</v>
+        <v>84.2</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="E80">
-        <v>33.299999999999997</v>
+        <v>51.2</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B81">
-        <v>987</v>
+        <v>544</v>
       </c>
       <c r="C81">
-        <v>82.6</v>
+        <v>86.7</v>
       </c>
       <c r="D81">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="E81">
-        <v>28.6</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="F81">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G81">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H81">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B82">
-        <v>1483</v>
+        <v>987</v>
       </c>
       <c r="C82">
-        <v>83.3</v>
+        <v>82.6</v>
       </c>
       <c r="D82">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E82">
-        <v>36.200000000000003</v>
+        <v>28.6</v>
       </c>
       <c r="F82">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="G82">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="H82">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B83">
-        <v>766</v>
+        <v>1483</v>
       </c>
       <c r="C83">
-        <v>76.400000000000006</v>
+        <v>83.3</v>
       </c>
       <c r="D83">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="E83">
-        <v>33.299999999999997</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="F83">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G83">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H83">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="B84">
-        <v>295</v>
+        <v>766</v>
       </c>
       <c r="C84">
-        <v>84.9</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="D84">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E84">
-        <v>66.7</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="F84">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G84">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H84">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>149</v>
       </c>
       <c r="B85">
-        <v>776</v>
+        <v>295</v>
       </c>
       <c r="C85">
-        <v>77</v>
+        <v>84.9</v>
       </c>
       <c r="D85">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="E85">
-        <v>47.1</v>
+        <v>66.7</v>
       </c>
       <c r="F85">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G85">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H85">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B86">
-        <v>797</v>
+        <v>776</v>
       </c>
       <c r="C86">
-        <v>79.599999999999994</v>
+        <v>77</v>
       </c>
       <c r="D86">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="E86">
-        <v>53.3</v>
+        <v>47.1</v>
       </c>
       <c r="F86">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G86">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H86">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B87">
-        <v>1488</v>
+        <v>797</v>
       </c>
       <c r="C87">
-        <v>79</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="D87">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="E87">
-        <v>48.7</v>
+        <v>53.3</v>
       </c>
       <c r="F87">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="G87">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H87">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B88">
-        <v>1317</v>
+        <v>1488</v>
       </c>
       <c r="C88">
-        <v>89.5</v>
+        <v>79</v>
       </c>
       <c r="D88">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="E88">
-        <v>50</v>
+        <v>48.7</v>
       </c>
       <c r="F88">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G88">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="H88">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B89">
-        <v>435</v>
+        <v>1317</v>
       </c>
       <c r="C89">
-        <v>88</v>
+        <v>89.5</v>
       </c>
       <c r="D89">
+        <v>23</v>
+      </c>
+      <c r="E89">
+        <v>50</v>
+      </c>
+      <c r="F89">
+        <v>15</v>
+      </c>
+      <c r="G89">
+        <v>13</v>
+      </c>
+      <c r="H89">
         <v>7</v>
-      </c>
-      <c r="E89">
-        <v>70</v>
-      </c>
-      <c r="F89">
-        <v>6</v>
-      </c>
-      <c r="G89">
-        <v>3</v>
-      </c>
-      <c r="H89">
-        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B90">
-        <v>599</v>
+        <v>435</v>
       </c>
       <c r="C90">
-        <v>88.6</v>
+        <v>88</v>
       </c>
       <c r="D90">
+        <v>7</v>
+      </c>
+      <c r="E90">
+        <v>70</v>
+      </c>
+      <c r="F90">
         <v>6</v>
-      </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
-      <c r="F90">
-        <v>3</v>
       </c>
       <c r="G90">
         <v>3</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B91">
-        <v>1436</v>
+        <v>599</v>
       </c>
       <c r="C91">
-        <v>83.8</v>
+        <v>88.6</v>
       </c>
       <c r="D91">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E91">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="F91">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G91">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H91">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B92">
-        <v>467</v>
+        <v>1436</v>
       </c>
       <c r="C92">
-        <v>87</v>
+        <v>83.8</v>
       </c>
       <c r="D92">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E92">
-        <v>57.1</v>
+        <v>42.9</v>
       </c>
       <c r="F92">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G92">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H92">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="B93">
-        <v>1083</v>
+        <v>467</v>
       </c>
       <c r="C93">
-        <v>75.900000000000006</v>
+        <v>87</v>
       </c>
       <c r="D93">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="E93">
-        <v>25.9</v>
+        <v>57.1</v>
       </c>
       <c r="F93">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G93">
         <v>10</v>
       </c>
       <c r="H93">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>150</v>
+      </c>
+      <c r="B94">
+        <v>1083</v>
+      </c>
+      <c r="C94">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="D94">
+        <v>47</v>
+      </c>
+      <c r="E94">
+        <v>25.9</v>
+      </c>
+      <c r="F94">
+        <v>19</v>
+      </c>
+      <c r="G94">
+        <v>10</v>
+      </c>
+      <c r="H94">
         <v>7</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B94" s="3">
-        <v>654</v>
-      </c>
-      <c r="C94" s="3">
-        <v>92</v>
-      </c>
-      <c r="D94" s="3">
-        <v>20</v>
-      </c>
-      <c r="E94" s="3">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="F94" s="3">
-        <v>8</v>
-      </c>
-      <c r="G94" s="3">
-        <v>10</v>
-      </c>
-      <c r="H94" s="3">
-        <v>4</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B95" s="3">
-        <v>746</v>
+        <v>654</v>
       </c>
       <c r="C95" s="3">
-        <v>89.4</v>
+        <v>92</v>
       </c>
       <c r="D95" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E95" s="3">
-        <v>44.1</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="F95" s="3">
+        <v>8</v>
+      </c>
+      <c r="G95" s="3">
         <v>10</v>
       </c>
-      <c r="G95" s="3">
-        <v>16</v>
-      </c>
       <c r="H95" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96" s="3">
-        <v>1379</v>
+        <v>746</v>
       </c>
       <c r="C96" s="3">
-        <v>93.9</v>
+        <v>89.4</v>
       </c>
       <c r="D96" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E96" s="3">
-        <v>69.2</v>
+        <v>44.1</v>
       </c>
       <c r="F96" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G96" s="3">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H96" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B97" s="3">
-        <v>795</v>
+        <v>1379</v>
       </c>
       <c r="C97" s="3">
-        <v>92.4</v>
+        <v>93.9</v>
       </c>
       <c r="D97" s="3">
+        <v>5</v>
+      </c>
+      <c r="E97" s="3">
+        <v>69.2</v>
+      </c>
+      <c r="F97" s="3">
+        <v>7</v>
+      </c>
+      <c r="G97" s="3">
         <v>26</v>
       </c>
-      <c r="E97" s="3">
-        <v>0</v>
-      </c>
-      <c r="F97" s="3">
-        <v>4</v>
-      </c>
-      <c r="G97" s="3">
-        <v>12</v>
-      </c>
       <c r="H97" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B98" s="3">
-        <v>726</v>
+        <v>795</v>
       </c>
       <c r="C98" s="3">
-        <v>92.9</v>
+        <v>92.4</v>
       </c>
       <c r="D98" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E98" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F98" s="3">
         <v>4</v>
       </c>
       <c r="G98" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H98" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B99" s="3">
-        <v>508</v>
+        <v>726</v>
       </c>
       <c r="C99" s="3">
-        <v>84.7</v>
+        <v>92.9</v>
       </c>
       <c r="D99" s="3">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E99" s="3">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="F99" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G99" s="3">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H99" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B100" s="3">
-        <v>839</v>
+        <v>508</v>
       </c>
       <c r="C100" s="3">
-        <v>85.9</v>
+        <v>84.7</v>
       </c>
       <c r="D100" s="3">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="E100" s="3">
-        <v>48.9</v>
+        <v>55.6</v>
       </c>
       <c r="F100" s="3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G100" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H100" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B101" s="3">
-        <v>926</v>
+        <v>839</v>
       </c>
       <c r="C101" s="3">
-        <v>85.6</v>
+        <v>85.9</v>
       </c>
       <c r="D101" s="3">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E101" s="3">
-        <v>40.4</v>
+        <v>48.9</v>
       </c>
       <c r="F101" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G101" s="3">
         <v>20</v>
       </c>
       <c r="H101" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B102" s="3">
-        <v>541</v>
+        <v>926</v>
       </c>
       <c r="C102" s="3">
-        <v>84.6</v>
+        <v>85.6</v>
       </c>
       <c r="D102" s="3">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="E102" s="3">
-        <v>36.1</v>
+        <v>40.4</v>
       </c>
       <c r="F102" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G102" s="3">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H102" s="3">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B103" s="3">
-        <v>1352</v>
+        <v>541</v>
       </c>
       <c r="C103" s="3">
-        <v>86.2</v>
+        <v>84.6</v>
       </c>
       <c r="D103" s="3">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="E103" s="3">
-        <v>56.2</v>
+        <v>36.1</v>
       </c>
       <c r="F103" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G103" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H103" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B104" s="3">
-        <v>1493</v>
+        <v>1352</v>
       </c>
       <c r="C104" s="3">
-        <v>78</v>
+        <v>86.2</v>
       </c>
       <c r="D104" s="3">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="E104" s="3">
-        <v>38</v>
+        <v>56.2</v>
       </c>
       <c r="F104" s="3">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G104" s="3">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H104" s="3">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B105" s="3">
-        <v>480</v>
+        <v>1493</v>
       </c>
       <c r="C105" s="3">
-        <v>79.3</v>
+        <v>78</v>
       </c>
       <c r="D105" s="3">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="E105" s="3">
-        <v>53.5</v>
+        <v>38</v>
       </c>
       <c r="F105" s="3">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="G105" s="3">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H105" s="3">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="B106" s="3">
-        <v>1328</v>
+        <v>480</v>
       </c>
       <c r="C106" s="3">
-        <v>82.2</v>
+        <v>79.3</v>
       </c>
       <c r="D106" s="3">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E106" s="3">
-        <v>52.2</v>
+        <v>53.5</v>
       </c>
       <c r="F106" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G106" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H106" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="B107" s="3">
-        <v>576</v>
+        <v>1328</v>
       </c>
       <c r="C107" s="3">
-        <v>74.3</v>
+        <v>82.2</v>
       </c>
       <c r="D107" s="3">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E107" s="3">
-        <v>31.2</v>
+        <v>52.2</v>
       </c>
       <c r="F107" s="3">
+        <v>15</v>
+      </c>
+      <c r="G107" s="3">
+        <v>16</v>
+      </c>
+      <c r="H107" s="3">
         <v>12</v>
-      </c>
-      <c r="G107" s="3">
-        <v>4</v>
-      </c>
-      <c r="H107" s="3">
-        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B108" s="3">
-        <v>1204</v>
+        <v>576</v>
       </c>
       <c r="C108" s="3">
-        <v>90.5</v>
+        <v>74.3</v>
       </c>
       <c r="D108" s="3">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E108" s="3">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="F108" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G108" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H108" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B109" s="3">
-        <v>1391</v>
+        <v>1204</v>
       </c>
       <c r="C109" s="3">
-        <v>93.1</v>
+        <v>90.5</v>
       </c>
       <c r="D109" s="3">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E109" s="3">
-        <v>66.7</v>
+        <v>30.8</v>
       </c>
       <c r="F109" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G109" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H109" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B110" s="3">
-        <v>314</v>
+        <v>1391</v>
       </c>
       <c r="C110" s="3">
-        <v>89.3</v>
+        <v>93.1</v>
       </c>
       <c r="D110" s="3">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E110" s="3">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="F110" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G110" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H110" s="3">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B111" s="3">
-        <v>892</v>
+        <v>314</v>
       </c>
       <c r="C111" s="3">
-        <v>90.9</v>
+        <v>89.3</v>
       </c>
       <c r="D111" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E111" s="3">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="F111" s="3">
+        <v>3</v>
+      </c>
+      <c r="G111" s="3">
+        <v>0</v>
+      </c>
+      <c r="H111" s="3">
         <v>5</v>
-      </c>
-      <c r="G111" s="3">
-        <v>18</v>
-      </c>
-      <c r="H111" s="3">
-        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B112" s="3">
-        <v>1391</v>
+        <v>892</v>
       </c>
       <c r="C112" s="3">
-        <v>82.2</v>
+        <v>90.9</v>
       </c>
       <c r="D112" s="3">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="E112" s="3">
-        <v>47.7</v>
+        <v>66.7</v>
       </c>
       <c r="F112" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G112" s="3">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H112" s="3">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B113" s="3">
-        <v>539</v>
+        <v>1391</v>
       </c>
       <c r="C113" s="3">
-        <v>86.8</v>
+        <v>82.2</v>
       </c>
       <c r="D113" s="3">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="E113" s="3">
-        <v>28.6</v>
+        <v>47.7</v>
       </c>
       <c r="F113" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G113" s="3">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H113" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B114" s="3">
-        <v>1048</v>
+        <v>539</v>
       </c>
       <c r="C114" s="3">
-        <v>83.3</v>
+        <v>86.8</v>
       </c>
       <c r="D114" s="3">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="E114" s="3">
-        <v>40</v>
+        <v>28.6</v>
       </c>
       <c r="F114" s="3">
+        <v>4</v>
+      </c>
+      <c r="G114" s="3">
+        <v>12</v>
+      </c>
+      <c r="H114" s="3">
         <v>6</v>
-      </c>
-      <c r="G114" s="3">
-        <v>16</v>
-      </c>
-      <c r="H114" s="3">
-        <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B115" s="3">
-        <v>1444</v>
+        <v>1048</v>
       </c>
       <c r="C115" s="3">
-        <v>85.2</v>
+        <v>83.3</v>
       </c>
       <c r="D115" s="3">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E115" s="3">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="F115" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G115" s="3">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H115" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B116" s="3">
-        <v>677</v>
+        <v>1444</v>
       </c>
       <c r="C116" s="3">
         <v>85.2</v>
       </c>
       <c r="D116" s="3">
+        <v>62</v>
+      </c>
+      <c r="E116" s="3">
+        <v>42.9</v>
+      </c>
+      <c r="F116" s="3">
         <v>20</v>
       </c>
-      <c r="E116" s="3">
-        <v>87.5</v>
-      </c>
-      <c r="F116" s="3">
-        <v>5</v>
-      </c>
       <c r="G116" s="3">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H116" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="B117" s="3">
-        <v>771</v>
+        <v>677</v>
       </c>
       <c r="C117" s="3">
-        <v>79.599999999999994</v>
+        <v>85.2</v>
       </c>
       <c r="D117" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E117" s="3">
-        <v>55.6</v>
+        <v>87.5</v>
       </c>
       <c r="F117" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G117" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H117" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="B118" s="3">
-        <v>978</v>
+        <v>771</v>
       </c>
       <c r="C118" s="3">
-        <v>76.8</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="D118" s="3">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="E118" s="3">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="F118" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G118" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H118" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B119" s="3">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="C119" s="3">
-        <v>86.1</v>
+        <v>76.8</v>
       </c>
       <c r="D119" s="3">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="E119" s="3">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F119" s="3">
         <v>7</v>
       </c>
       <c r="G119" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H119" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B120" s="3">
-        <v>1050</v>
+        <v>984</v>
       </c>
       <c r="C120" s="3">
-        <v>83.7</v>
+        <v>86.1</v>
       </c>
       <c r="D120" s="3">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="E120" s="3">
-        <v>48.4</v>
+        <v>44.4</v>
       </c>
       <c r="F120" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G120" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H120" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B121" s="3">
-        <v>694</v>
+        <v>1050</v>
       </c>
       <c r="C121" s="3">
-        <v>87</v>
+        <v>83.7</v>
       </c>
       <c r="D121" s="3">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="E121" s="3">
-        <v>66.7</v>
+        <v>48.4</v>
       </c>
       <c r="F121" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G121" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H121" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="B122" s="3">
-        <v>1425</v>
+        <v>694</v>
       </c>
       <c r="C122" s="3">
-        <v>86.5</v>
+        <v>87</v>
       </c>
       <c r="D122" s="3">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E122" s="3">
-        <v>40.9</v>
+        <v>66.7</v>
       </c>
       <c r="F122" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G122" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H122" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="B123" s="3">
-        <v>655</v>
+        <v>1425</v>
       </c>
       <c r="C123" s="3">
-        <v>90.5</v>
+        <v>86.5</v>
       </c>
       <c r="D123" s="3">
+        <v>19</v>
+      </c>
+      <c r="E123" s="3">
+        <v>40.9</v>
+      </c>
+      <c r="F123" s="3">
+        <v>15</v>
+      </c>
+      <c r="G123" s="3">
+        <v>22</v>
+      </c>
+      <c r="H123" s="3">
         <v>18</v>
-      </c>
-      <c r="E123" s="3">
-        <v>42.9</v>
-      </c>
-      <c r="F123" s="3">
-        <v>2</v>
-      </c>
-      <c r="G123" s="3">
-        <v>7</v>
-      </c>
-      <c r="H123" s="3">
-        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B124" s="3">
-        <v>1291</v>
+        <v>655</v>
       </c>
       <c r="C124" s="3">
-        <v>85.6</v>
+        <v>90.5</v>
       </c>
       <c r="D124" s="3">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="E124" s="3">
-        <v>37.5</v>
+        <v>42.9</v>
       </c>
       <c r="F124" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G124" s="3">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H124" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B125" s="3">
-        <v>462</v>
+        <v>1291</v>
       </c>
       <c r="C125" s="3">
-        <v>86.3</v>
+        <v>85.6</v>
       </c>
       <c r="D125" s="3">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="E125" s="3">
-        <v>11.1</v>
+        <v>37.5</v>
       </c>
       <c r="F125" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G125" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="H125" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B126" s="3">
-        <v>1112</v>
+        <v>462</v>
       </c>
       <c r="C126" s="3">
-        <v>92.8</v>
+        <v>86.3</v>
       </c>
       <c r="D126" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E126" s="3">
-        <v>100</v>
+        <v>11.1</v>
       </c>
       <c r="F126" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G126" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H126" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="B127" s="3">
-        <v>743</v>
+        <v>1112</v>
       </c>
       <c r="C127" s="3">
-        <v>85.9</v>
+        <v>92.8</v>
       </c>
       <c r="D127" s="3">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="E127" s="3">
-        <v>30.3</v>
+        <v>100</v>
       </c>
       <c r="F127" s="3">
+        <v>9</v>
+      </c>
+      <c r="G127" s="3">
         <v>11</v>
       </c>
-      <c r="G127" s="3">
-        <v>14</v>
-      </c>
       <c r="H127" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="B128" s="3">
-        <v>1121</v>
+        <v>743</v>
       </c>
       <c r="C128" s="3">
-        <v>92.3</v>
+        <v>85.9</v>
       </c>
       <c r="D128" s="3">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="E128" s="3">
-        <v>66.7</v>
+        <v>30.3</v>
       </c>
       <c r="F128" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G128" s="3">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H128" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B129" s="3">
-        <v>805</v>
+        <v>1121</v>
       </c>
       <c r="C129" s="3">
-        <v>88.4</v>
+        <v>92.3</v>
       </c>
       <c r="D129" s="3">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="E129" s="3">
-        <v>47.8</v>
+        <v>66.7</v>
       </c>
       <c r="F129" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G129" s="3">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H129" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B130" s="3">
-        <v>1460</v>
+        <v>805</v>
       </c>
       <c r="C130" s="3">
-        <v>85.1</v>
+        <v>88.4</v>
       </c>
       <c r="D130" s="3">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="E130" s="3">
-        <v>42.7</v>
+        <v>47.8</v>
       </c>
       <c r="F130" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G130" s="3">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H130" s="3">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B131" s="3">
+        <v>1460</v>
+      </c>
+      <c r="C131" s="3">
+        <v>85.1</v>
+      </c>
+      <c r="D131" s="3">
+        <v>144</v>
+      </c>
+      <c r="E131" s="3">
+        <v>42.7</v>
+      </c>
+      <c r="F131" s="3">
+        <v>19</v>
+      </c>
+      <c r="G131" s="3">
+        <v>50</v>
+      </c>
+      <c r="H131" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A132" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B131" s="3">
+      <c r="B132" s="3">
         <v>1525</v>
       </c>
-      <c r="C131" s="3">
+      <c r="C132" s="3">
         <v>85.8</v>
       </c>
-      <c r="D131" s="3">
+      <c r="D132" s="3">
         <v>139</v>
       </c>
-      <c r="E131" s="3">
+      <c r="E132" s="3">
         <v>46.6</v>
       </c>
-      <c r="F131" s="3">
+      <c r="F132" s="3">
         <v>28</v>
       </c>
-      <c r="G131" s="3">
+      <c r="G132" s="3">
         <v>36</v>
       </c>
-      <c r="H131" s="3">
+      <c r="H132" s="3">
         <v>34</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
-        <v>128</v>
-      </c>
-      <c r="B132" s="3">
-        <v>778</v>
-      </c>
-      <c r="C132" s="3">
-        <v>82.1</v>
-      </c>
-      <c r="D132" s="3">
-        <v>14</v>
-      </c>
-      <c r="E132" s="3">
-        <v>47.1</v>
-      </c>
-      <c r="F132" s="3">
-        <v>8</v>
-      </c>
-      <c r="G132" s="3">
-        <v>13</v>
-      </c>
-      <c r="H132" s="3">
-        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B133" s="3">
-        <v>1422</v>
+        <v>778</v>
       </c>
       <c r="C133" s="3">
-        <v>86.4</v>
+        <v>82.1</v>
       </c>
       <c r="D133" s="3">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E133" s="3">
-        <v>54.3</v>
+        <v>47.1</v>
       </c>
       <c r="F133" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G133" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H133" s="3">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B134" s="3">
-        <v>683</v>
+        <v>1422</v>
       </c>
       <c r="C134" s="3">
-        <v>85.1</v>
+        <v>86.4</v>
       </c>
       <c r="D134" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E134" s="3">
-        <v>45.5</v>
+        <v>54.3</v>
       </c>
       <c r="F134" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G134" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H134" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B135" s="3">
-        <v>570</v>
+        <v>683</v>
       </c>
       <c r="C135" s="3">
-        <v>86.1</v>
+        <v>85.1</v>
       </c>
       <c r="D135" s="3">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E135" s="3">
-        <v>48.6</v>
+        <v>45.5</v>
       </c>
       <c r="F135" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G135" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H135" s="3">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B136" s="3">
-        <v>1389</v>
+        <v>570</v>
       </c>
       <c r="C136" s="3">
-        <v>74.400000000000006</v>
+        <v>86.1</v>
       </c>
       <c r="D136" s="3">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="E136" s="3">
-        <v>50</v>
+        <v>48.6</v>
       </c>
       <c r="F136" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G136" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H136" s="3">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B137" s="3">
-        <v>833</v>
+        <v>1389</v>
       </c>
       <c r="C137" s="3">
-        <v>72.5</v>
+        <v>74.400000000000006</v>
       </c>
       <c r="D137" s="3">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="E137" s="3">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="F137" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G137" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H137" s="3">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B138" s="3">
-        <v>1048</v>
+        <v>833</v>
       </c>
       <c r="C138" s="3">
-        <v>84.1</v>
+        <v>72.5</v>
       </c>
       <c r="D138" s="3">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E138" s="3">
-        <v>58.5</v>
+        <v>37.5</v>
       </c>
       <c r="F138" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G138" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H138" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B139" s="3">
-        <v>231</v>
+        <v>1048</v>
       </c>
       <c r="C139" s="3">
-        <v>83.3</v>
+        <v>84.1</v>
       </c>
       <c r="D139" s="3">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="E139" s="3">
-        <v>33.299999999999997</v>
+        <v>58.5</v>
       </c>
       <c r="F139" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G139" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H139" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B140" s="3">
-        <v>800</v>
+        <v>231</v>
       </c>
       <c r="C140" s="3">
         <v>83.3</v>
       </c>
       <c r="D140" s="3">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E140" s="3">
-        <v>44.4</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="F140" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G140" s="3">
         <v>9</v>
       </c>
       <c r="H140" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B141" s="3">
-        <v>1119</v>
+        <v>800</v>
       </c>
       <c r="C141" s="3">
-        <v>76.3</v>
+        <v>83.3</v>
       </c>
       <c r="D141" s="3">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="E141" s="3">
-        <v>41.7</v>
+        <v>44.4</v>
       </c>
       <c r="F141" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G141" s="3">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H141" s="3">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B142" s="3">
-        <v>1170</v>
+        <v>1119</v>
       </c>
       <c r="C142" s="3">
-        <v>70.7</v>
+        <v>76.3</v>
       </c>
       <c r="D142" s="3">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E142" s="3">
-        <v>40.9</v>
+        <v>41.7</v>
       </c>
       <c r="F142" s="3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G142" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H142" s="3">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B143" s="3">
-        <v>1516</v>
+        <v>1170</v>
       </c>
       <c r="C143" s="3">
-        <v>88.2</v>
+        <v>70.7</v>
       </c>
       <c r="D143" s="3">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="E143" s="3">
-        <v>9</v>
+        <v>40.9</v>
       </c>
       <c r="F143" s="3">
         <v>9</v>
       </c>
       <c r="G143" s="3">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H143" s="3">
         <v>9</v>
@@ -4611,183 +4614,209 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B144" s="3">
-        <v>674</v>
+        <v>1516</v>
       </c>
       <c r="C144" s="3">
-        <v>85.4</v>
+        <v>88.2</v>
       </c>
       <c r="D144" s="3">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E144" s="3">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="F144" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G144" s="3">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H144" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B145" s="3">
-        <v>1088</v>
+        <v>674</v>
       </c>
       <c r="C145" s="3">
-        <v>75.599999999999994</v>
+        <v>85.4</v>
       </c>
       <c r="D145" s="3">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="E145" s="3">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F145" s="3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G145" s="3">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H145" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B146" s="3">
-        <v>632</v>
+        <v>1088</v>
       </c>
       <c r="C146" s="3">
-        <v>72.900000000000006</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="D146" s="3">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="E146" s="3">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F146" s="3">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G146" s="3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H146" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B147" s="3">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="C147" s="3">
-        <v>79.7</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="D147" s="3">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E147" s="3">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="F147" s="3">
         <v>12</v>
       </c>
       <c r="G147" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H147" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B148" s="3">
-        <v>420</v>
+        <v>626</v>
       </c>
       <c r="C148" s="3">
-        <v>77.5</v>
+        <v>79.7</v>
       </c>
       <c r="D148" s="3">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E148" s="3">
-        <v>33.299999999999997</v>
+        <v>32</v>
       </c>
       <c r="F148" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G148" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H148" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B149" s="3">
-        <v>681</v>
+        <v>420</v>
       </c>
       <c r="C149" s="3">
-        <v>80.5</v>
+        <v>77.5</v>
       </c>
       <c r="D149" s="3">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E149" s="3">
-        <v>68.400000000000006</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="F149" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G149" s="3">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H149" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
+        <v>145</v>
+      </c>
+      <c r="B150" s="3">
+        <v>681</v>
+      </c>
+      <c r="C150" s="3">
+        <v>80.5</v>
+      </c>
+      <c r="D150" s="3">
+        <v>34</v>
+      </c>
+      <c r="E150" s="3">
+        <v>68.400000000000006</v>
+      </c>
+      <c r="F150" s="3">
+        <v>7</v>
+      </c>
+      <c r="G150" s="3">
+        <v>19</v>
+      </c>
+      <c r="H150" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
         <v>156</v>
       </c>
-      <c r="B150" s="3">
+      <c r="B151" s="3">
         <v>1098</v>
       </c>
-      <c r="C150" s="3">
+      <c r="C151" s="3">
         <v>83.5</v>
       </c>
-      <c r="D150" s="3">
+      <c r="D151" s="3">
         <v>87</v>
       </c>
-      <c r="E150" s="3">
+      <c r="E151" s="3">
         <v>55.8</v>
       </c>
-      <c r="F150" s="3">
+      <c r="F151" s="3">
         <v>27</v>
       </c>
-      <c r="G150" s="3">
+      <c r="G151" s="3">
         <v>22</v>
       </c>
-      <c r="H150" s="3">
+      <c r="H151" s="3">
         <v>53</v>
       </c>
     </row>

--- a/Unisport-FutbolDataAcademy/Unisport/ModuloDos/participacion_en_el_juego.xlsx
+++ b/Unisport-FutbolDataAcademy/Unisport/ModuloDos/participacion_en_el_juego.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidvh10/Desktop/Mis Cosas/RepositorioCodigo/Unisport-FutbolDataAcademy/Unisport/ModuloDos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B93C4C1-5104-4348-A0DB-35DC1A442C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{259AFA6F-4CB8-5D45-91BA-1F633C00AEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7420" yWindow="2660" windowWidth="28040" windowHeight="17440" xr2:uid="{D01ACE11-2F64-D442-81D6-1A9F9F4A7DB9}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="158">
   <si>
     <t>Jugador</t>
   </si>
@@ -883,7 +883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32C8081-2E1E-E04A-BC92-1E8D2679565E}">
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
@@ -4820,6 +4820,656 @@
         <v>53</v>
       </c>
     </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>7</v>
+      </c>
+      <c r="B152">
+        <v>638</v>
+      </c>
+      <c r="C152">
+        <v>90.7</v>
+      </c>
+      <c r="D152">
+        <v>42</v>
+      </c>
+      <c r="E152">
+        <v>38.5</v>
+      </c>
+      <c r="F152">
+        <v>17</v>
+      </c>
+      <c r="G152">
+        <v>9</v>
+      </c>
+      <c r="H152">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>12</v>
+      </c>
+      <c r="B153">
+        <v>703</v>
+      </c>
+      <c r="C153">
+        <v>82</v>
+      </c>
+      <c r="D153">
+        <v>22</v>
+      </c>
+      <c r="E153">
+        <v>35</v>
+      </c>
+      <c r="F153">
+        <v>11</v>
+      </c>
+      <c r="G153">
+        <v>20</v>
+      </c>
+      <c r="H153">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>16</v>
+      </c>
+      <c r="B154">
+        <v>812</v>
+      </c>
+      <c r="C154">
+        <v>85.8</v>
+      </c>
+      <c r="D154">
+        <v>46</v>
+      </c>
+      <c r="E154">
+        <v>57.6</v>
+      </c>
+      <c r="F154">
+        <v>13</v>
+      </c>
+      <c r="G154">
+        <v>17</v>
+      </c>
+      <c r="H154">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>25</v>
+      </c>
+      <c r="B155">
+        <v>759</v>
+      </c>
+      <c r="C155">
+        <v>79.2</v>
+      </c>
+      <c r="D155">
+        <v>29</v>
+      </c>
+      <c r="E155">
+        <v>53.8</v>
+      </c>
+      <c r="F155">
+        <v>11</v>
+      </c>
+      <c r="G155">
+        <v>22</v>
+      </c>
+      <c r="H155">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>28</v>
+      </c>
+      <c r="B156">
+        <v>644</v>
+      </c>
+      <c r="C156">
+        <v>71.2</v>
+      </c>
+      <c r="D156">
+        <v>47</v>
+      </c>
+      <c r="E156">
+        <v>45</v>
+      </c>
+      <c r="F156">
+        <v>13</v>
+      </c>
+      <c r="G156">
+        <v>5</v>
+      </c>
+      <c r="H156">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>39</v>
+      </c>
+      <c r="B157">
+        <v>959</v>
+      </c>
+      <c r="C157">
+        <v>84.3</v>
+      </c>
+      <c r="D157">
+        <v>88</v>
+      </c>
+      <c r="E157">
+        <v>43.3</v>
+      </c>
+      <c r="F157">
+        <v>21</v>
+      </c>
+      <c r="G157">
+        <v>33</v>
+      </c>
+      <c r="H157">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>47</v>
+      </c>
+      <c r="B158">
+        <v>2004</v>
+      </c>
+      <c r="C158">
+        <v>87.2</v>
+      </c>
+      <c r="D158">
+        <v>16</v>
+      </c>
+      <c r="E158">
+        <v>41.7</v>
+      </c>
+      <c r="F158">
+        <v>3</v>
+      </c>
+      <c r="G158">
+        <v>13</v>
+      </c>
+      <c r="H158">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>53</v>
+      </c>
+      <c r="B159">
+        <v>1258</v>
+      </c>
+      <c r="C159">
+        <v>74.8</v>
+      </c>
+      <c r="D159">
+        <v>90</v>
+      </c>
+      <c r="E159">
+        <v>52.9</v>
+      </c>
+      <c r="F159">
+        <v>19</v>
+      </c>
+      <c r="G159">
+        <v>14</v>
+      </c>
+      <c r="H159">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>61</v>
+      </c>
+      <c r="B160">
+        <v>1331</v>
+      </c>
+      <c r="C160">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="D160">
+        <v>30</v>
+      </c>
+      <c r="E160">
+        <v>56.4</v>
+      </c>
+      <c r="F160">
+        <v>10</v>
+      </c>
+      <c r="G160">
+        <v>5</v>
+      </c>
+      <c r="H160">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>64</v>
+      </c>
+      <c r="B161">
+        <v>930</v>
+      </c>
+      <c r="C161">
+        <v>72.5</v>
+      </c>
+      <c r="D161">
+        <v>38</v>
+      </c>
+      <c r="E161">
+        <v>35</v>
+      </c>
+      <c r="F161">
+        <v>17</v>
+      </c>
+      <c r="G161">
+        <v>12</v>
+      </c>
+      <c r="H161">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>70</v>
+      </c>
+      <c r="B162">
+        <v>1537</v>
+      </c>
+      <c r="C162">
+        <v>81.5</v>
+      </c>
+      <c r="D162">
+        <v>57</v>
+      </c>
+      <c r="E162">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="F162">
+        <v>5</v>
+      </c>
+      <c r="G162">
+        <v>54</v>
+      </c>
+      <c r="H162">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>75</v>
+      </c>
+      <c r="B163">
+        <v>1803</v>
+      </c>
+      <c r="C163">
+        <v>87.9</v>
+      </c>
+      <c r="D163">
+        <v>65</v>
+      </c>
+      <c r="E163">
+        <v>48.6</v>
+      </c>
+      <c r="F163">
+        <v>42</v>
+      </c>
+      <c r="G163">
+        <v>15</v>
+      </c>
+      <c r="H163">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>79</v>
+      </c>
+      <c r="B164">
+        <v>1248</v>
+      </c>
+      <c r="C164">
+        <v>90.7</v>
+      </c>
+      <c r="D164">
+        <v>17</v>
+      </c>
+      <c r="E164">
+        <v>40</v>
+      </c>
+      <c r="F164">
+        <v>2</v>
+      </c>
+      <c r="G164">
+        <v>14</v>
+      </c>
+      <c r="H164">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>83</v>
+      </c>
+      <c r="B165">
+        <v>987</v>
+      </c>
+      <c r="C165">
+        <v>82.6</v>
+      </c>
+      <c r="D165">
+        <v>72</v>
+      </c>
+      <c r="E165">
+        <v>28.6</v>
+      </c>
+      <c r="F165">
+        <v>18</v>
+      </c>
+      <c r="G165">
+        <v>40</v>
+      </c>
+      <c r="H165">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>87</v>
+      </c>
+      <c r="B166">
+        <v>797</v>
+      </c>
+      <c r="C166">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="D166">
+        <v>66</v>
+      </c>
+      <c r="E166">
+        <v>53.3</v>
+      </c>
+      <c r="F166">
+        <v>11</v>
+      </c>
+      <c r="G166">
+        <v>17</v>
+      </c>
+      <c r="H166">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>92</v>
+      </c>
+      <c r="B167">
+        <v>1436</v>
+      </c>
+      <c r="C167">
+        <v>83.8</v>
+      </c>
+      <c r="D167">
+        <v>5</v>
+      </c>
+      <c r="E167">
+        <v>42.9</v>
+      </c>
+      <c r="F167">
+        <v>4</v>
+      </c>
+      <c r="G167">
+        <v>16</v>
+      </c>
+      <c r="H167">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A168" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B168" s="3">
+        <v>746</v>
+      </c>
+      <c r="C168" s="3">
+        <v>89.4</v>
+      </c>
+      <c r="D168" s="3">
+        <v>30</v>
+      </c>
+      <c r="E168" s="3">
+        <v>44.1</v>
+      </c>
+      <c r="F168" s="3">
+        <v>10</v>
+      </c>
+      <c r="G168" s="3">
+        <v>16</v>
+      </c>
+      <c r="H168" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A169" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B169" s="3">
+        <v>541</v>
+      </c>
+      <c r="C169" s="3">
+        <v>84.6</v>
+      </c>
+      <c r="D169" s="3">
+        <v>49</v>
+      </c>
+      <c r="E169" s="3">
+        <v>36.1</v>
+      </c>
+      <c r="F169" s="3">
+        <v>15</v>
+      </c>
+      <c r="G169" s="3">
+        <v>14</v>
+      </c>
+      <c r="H169" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A170" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B170" s="3">
+        <v>576</v>
+      </c>
+      <c r="C170" s="3">
+        <v>74.3</v>
+      </c>
+      <c r="D170" s="3">
+        <v>38</v>
+      </c>
+      <c r="E170" s="3">
+        <v>31.2</v>
+      </c>
+      <c r="F170" s="3">
+        <v>12</v>
+      </c>
+      <c r="G170" s="3">
+        <v>4</v>
+      </c>
+      <c r="H170" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A171" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B171" s="3">
+        <v>677</v>
+      </c>
+      <c r="C171" s="3">
+        <v>85.2</v>
+      </c>
+      <c r="D171" s="3">
+        <v>20</v>
+      </c>
+      <c r="E171" s="3">
+        <v>87.5</v>
+      </c>
+      <c r="F171" s="3">
+        <v>5</v>
+      </c>
+      <c r="G171" s="3">
+        <v>8</v>
+      </c>
+      <c r="H171" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A172" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B172" s="3">
+        <v>1425</v>
+      </c>
+      <c r="C172" s="3">
+        <v>86.5</v>
+      </c>
+      <c r="D172" s="3">
+        <v>19</v>
+      </c>
+      <c r="E172" s="3">
+        <v>40.9</v>
+      </c>
+      <c r="F172" s="3">
+        <v>15</v>
+      </c>
+      <c r="G172" s="3">
+        <v>22</v>
+      </c>
+      <c r="H172" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A173" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B173" s="3">
+        <v>1121</v>
+      </c>
+      <c r="C173" s="3">
+        <v>92.3</v>
+      </c>
+      <c r="D173" s="3">
+        <v>15</v>
+      </c>
+      <c r="E173" s="3">
+        <v>66.7</v>
+      </c>
+      <c r="F173" s="3">
+        <v>3</v>
+      </c>
+      <c r="G173" s="3">
+        <v>29</v>
+      </c>
+      <c r="H173" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>129</v>
+      </c>
+      <c r="B174" s="3">
+        <v>1422</v>
+      </c>
+      <c r="C174" s="3">
+        <v>86.4</v>
+      </c>
+      <c r="D174" s="3">
+        <v>26</v>
+      </c>
+      <c r="E174" s="3">
+        <v>54.3</v>
+      </c>
+      <c r="F174" s="3">
+        <v>6</v>
+      </c>
+      <c r="G174" s="3">
+        <v>14</v>
+      </c>
+      <c r="H174" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>137</v>
+      </c>
+      <c r="B175" s="3">
+        <v>1119</v>
+      </c>
+      <c r="C175" s="3">
+        <v>76.3</v>
+      </c>
+      <c r="D175" s="3">
+        <v>53</v>
+      </c>
+      <c r="E175" s="3">
+        <v>41.7</v>
+      </c>
+      <c r="F175" s="3">
+        <v>19</v>
+      </c>
+      <c r="G175" s="3">
+        <v>20</v>
+      </c>
+      <c r="H175" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>144</v>
+      </c>
+      <c r="B176" s="3">
+        <v>420</v>
+      </c>
+      <c r="C176" s="3">
+        <v>77.5</v>
+      </c>
+      <c r="D176" s="3">
+        <v>20</v>
+      </c>
+      <c r="E176" s="3">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="F176" s="3">
+        <v>6</v>
+      </c>
+      <c r="G176" s="3">
+        <v>5</v>
+      </c>
+      <c r="H176" s="3">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
